--- a/data/samples/samples/苏48-12-66X_D03_2026-03-03.xlsx
+++ b/data/samples/samples/苏48-12-66X_D03_2026-03-03.xlsx
@@ -1053,7 +1053,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>08:00 08:45 接单根，耗时 12 分钟。</t>
+          <t>08:45 08:45 接单根，耗时 12 分钟。</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>15:00 15:45 短起下检查井眼，返砂正常。</t>
+          <t>15:45 15:45 短起下检查井眼，返砂正常。</t>
         </is>
       </c>
     </row>
